--- a/data/data_xlsx/arid_c14.xlsx
+++ b/data/data_xlsx/arid_c14.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q1203"/>
+  <dimension ref="A1:Q1211"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -77583,6 +77583,396 @@
         </is>
       </c>
     </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Coast</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>Copaca 1</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>UGAM 15623</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Copaca 1, Individuo 1</t>
+        </is>
+      </c>
+      <c r="G1204">
+        <v>5200</v>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M1204" t="inlineStr">
+        <is>
+          <t>Bone collagen</t>
+        </is>
+      </c>
+      <c r="P1204" t="inlineStr">
+        <is>
+          <t>humans</t>
+        </is>
+      </c>
+      <c r="Q1204" t="inlineStr">
+        <is>
+          <t>Andrade et al. (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Coast</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Copaca 1</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>UGAM 15624</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Copaca 1, Individuo 2</t>
+        </is>
+      </c>
+      <c r="G1205">
+        <v>5220</v>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M1205" t="inlineStr">
+        <is>
+          <t>Bone collagen</t>
+        </is>
+      </c>
+      <c r="P1205" t="inlineStr">
+        <is>
+          <t>humans</t>
+        </is>
+      </c>
+      <c r="Q1205" t="inlineStr">
+        <is>
+          <t>Andrade et al. (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Coast</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Copaca 1</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>UGAM 15625</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Copaca 1, Individuo 3</t>
+        </is>
+      </c>
+      <c r="G1206">
+        <v>5140</v>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M1206" t="inlineStr">
+        <is>
+          <t>Bone collagen</t>
+        </is>
+      </c>
+      <c r="P1206" t="inlineStr">
+        <is>
+          <t>humans</t>
+        </is>
+      </c>
+      <c r="Q1206" t="inlineStr">
+        <is>
+          <t>Andrade et al. (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Coast</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>Copaca 1</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>UGAM 15626</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Copaca 1, Individuo 4</t>
+        </is>
+      </c>
+      <c r="G1207">
+        <v>5150</v>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M1207" t="inlineStr">
+        <is>
+          <t>Bone collagen</t>
+        </is>
+      </c>
+      <c r="P1207" t="inlineStr">
+        <is>
+          <t>humans</t>
+        </is>
+      </c>
+      <c r="Q1207" t="inlineStr">
+        <is>
+          <t>Andrade et al. (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Precordillera</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>Alero Ampahuasi</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>UGAMS 16083</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Adolescente (hueso)</t>
+        </is>
+      </c>
+      <c r="G1208">
+        <v>2730</v>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M1208" t="inlineStr">
+        <is>
+          <t>Colageno oseo</t>
+        </is>
+      </c>
+      <c r="P1208" t="inlineStr">
+        <is>
+          <t>humans</t>
+        </is>
+      </c>
+      <c r="Q1208" t="inlineStr">
+        <is>
+          <t>De Souza et al. (2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Precordillera</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>Alero Ampahuasi</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>UGAMS 16081</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Perinato (cabello)</t>
+        </is>
+      </c>
+      <c r="G1209">
+        <v>2770</v>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M1209" t="inlineStr">
+        <is>
+          <t>Pelo humano</t>
+        </is>
+      </c>
+      <c r="P1209" t="inlineStr">
+        <is>
+          <t>humans</t>
+        </is>
+      </c>
+      <c r="Q1209" t="inlineStr">
+        <is>
+          <t>De Souza et al. (2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Precordillera</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>Alero Ampahuasi</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Turbante</t>
+        </is>
+      </c>
+      <c r="G1210">
+        <v>2450</v>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M1210" t="inlineStr">
+        <is>
+          <t>Fibra de camelido</t>
+        </is>
+      </c>
+      <c r="P1210" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="Q1210" t="inlineStr">
+        <is>
+          <t>De Souza et al. (2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Precordillera</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>Alero Ampahuasi</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Cesto</t>
+        </is>
+      </c>
+      <c r="G1211">
+        <v>2410</v>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M1211" t="inlineStr">
+        <is>
+          <t>Fibra vegetal</t>
+        </is>
+      </c>
+      <c r="P1211" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="Q1211" t="inlineStr">
+        <is>
+          <t>De Souza et al. (2019)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
